--- a/AAII_Financials/Quarterly/AVIFY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AVIFY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="92">
   <si>
     <t>AVIFY</t>
   </si>
@@ -656,178 +656,182 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -870,86 +874,89 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3">
         <v>1466800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1262200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1265800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1286400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1430100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1231000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1221600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1268100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1285500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1201400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1268900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1270800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1464000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1427400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1415000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1426800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1426300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1321400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1355500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1314000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1293000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1210600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1226300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1198800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1274700</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1144400</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -992,86 +999,89 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>1006000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>865300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>850000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>871600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>997800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>802900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>798100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>850400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>859200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>764000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>803800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>793600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>941900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>850000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>862800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>889700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>909000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>816600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>812100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>761400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>770400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>692900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>707100</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>712400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>773700</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>640700</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1114,86 +1124,89 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3">
         <v>460800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>396900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>415900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>414800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>432300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>428100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>423500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>417700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>426200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>437400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>465100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>477200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>522100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>577500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>552200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>537100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>517300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>504800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>543400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>552600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>522600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>517800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>519100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>486400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>501000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>503700</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1236,8 +1249,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1358,8 +1372,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1480,8 +1497,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1524,8 +1544,8 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1602,8 +1622,11 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1646,8 +1669,8 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1724,8 +1747,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1765,8 +1791,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1809,86 +1836,89 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3">
         <v>1171400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1019100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1009000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1028900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1163400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>955000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>945100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1002300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1027300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>937000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>984800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>979700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1184800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1047800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1085400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1088900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1126400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1025100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1007800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>956400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>962200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>897300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>913500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>874900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1016200</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>861800</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1931,86 +1961,89 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3">
         <v>295400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>243100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>256800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>257500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>266800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>276000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>276500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>265800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>258100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>264400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>284200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>291100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>279200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>379700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>329700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>337800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>299900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>296400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>347700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>357600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>330800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>313300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>312800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>323900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>258500</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>282600</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2053,8 +2086,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2097,86 +2131,89 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>18000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>10300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-9100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>11300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>11100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>14800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>6900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>7300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>1400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>4700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>600</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2219,86 +2256,89 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>708500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>599500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>623200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>640500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>661900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>657400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>670000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>622600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>632600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>637300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>685300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>672200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>578700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>682900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>627500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>631800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>587600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>564200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>617500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>612400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>587600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>557500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>543300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>542000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>469800</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>477900</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2341,86 +2381,89 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3">
         <v>39000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>35300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>37000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>37500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>38800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>41100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>41700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>38300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>37900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>41700</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>46400</v>
       </c>
       <c r="AB22" s="3">
         <v>46400</v>
       </c>
       <c r="AC22" s="3">
+        <v>46400</v>
+      </c>
+      <c r="AD22" s="3">
         <v>35100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>38100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>38300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>40100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>41200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>40100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>41400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>41500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>42200</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>42000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>41600</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>39900</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>41100</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>40400</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2463,86 +2506,89 @@
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3">
         <v>274400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>203200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>217300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>223100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>238300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>225800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>246100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>224600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>231400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>222600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>252600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>240000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>251000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>339300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>298700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>299900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>261100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>255600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>308900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>311600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>289100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>272700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>271700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>288800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>218100</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>244300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2585,86 +2631,89 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3">
         <v>52600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>38500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>41000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>43800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>43300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>40700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>44900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>40800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>31500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>35000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>42400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>39600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>39100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>58500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>49700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>50200</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>42200</v>
       </c>
       <c r="AH24" s="3">
         <v>42200</v>
       </c>
       <c r="AI24" s="3">
+        <v>42200</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>51300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>53200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>47500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>38300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>45300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>51500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>18300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>42300</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2785,8 +2834,11 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2829,86 +2881,89 @@
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3">
         <v>221800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>164700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>176300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>179300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>195000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>185200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>201200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>183700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>199900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>187600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>210200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>200400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>211900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>280800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>248900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>249700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>218800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>213400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>257600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>258300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>241700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>234400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>226400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>237300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>199700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>202000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2951,86 +3006,89 @@
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3">
         <v>221800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>164700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>176300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>179300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>195000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>185200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>201200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>183700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>199900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>187600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>210200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>200400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>211900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>280800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>248900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>249700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>218800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>213400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>257000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>258000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>241600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>234400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>226400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>237300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>199500</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>201400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3151,8 +3209,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3195,8 +3256,8 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -3273,8 +3334,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3395,8 +3459,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3517,8 +3584,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3561,86 +3631,89 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>-18000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-10300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>9100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-11300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-14800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>4700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-7300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>4500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-4700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-600</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3683,86 +3756,89 @@
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3">
         <v>221800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>164700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>176300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>179300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>195000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>185200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>201200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>183700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>199900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>187600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>210200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>200400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>211900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>280800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>248900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>249700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>218800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>213400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>257000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>258000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>241600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>234400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>226400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>237300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>199500</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>201400</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3883,8 +3959,11 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3927,213 +4006,219 @@
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3">
         <v>221800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>164700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>176300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>179300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>195000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>185200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>201200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>183700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>199900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>187600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>210200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>200400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>211900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>280800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>248900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>249700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>218800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>213400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>257000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>258000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>241600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>234400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>226400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>237300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>199500</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>201400</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4176,8 +4261,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4220,148 +4306,152 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>425300</v>
+      </c>
+      <c r="E41" s="3">
         <v>2086500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>803900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>468800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>637800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1031900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>658700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>401200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>384600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>640600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>428900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>432500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>384700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>366600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>271500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>255500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>283700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>465600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>361900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>329300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>484800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>490800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>513900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>479100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>775600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>906300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>588900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>360000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>359500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>676000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>290000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>258800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>242500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>272800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>334200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>296500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>298900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>311000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>346300</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>335300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E42" s="3">
         <v>18900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>19500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>19000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>18000</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -4384,46 +4474,46 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>33600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>14700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>6100</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
-      </c>
-      <c r="W42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>8</v>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
       </c>
       <c r="AB42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
@@ -4431,895 +4521,919 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG42" s="3">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH42" s="3">
         <v>200</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI42" s="3">
+      <c r="AI42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK42" s="3">
+      <c r="AK42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL42" s="3">
         <v>2600</v>
       </c>
-      <c r="AL42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM42" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AO42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP42" s="3">
         <v>7300</v>
       </c>
-      <c r="AP42" s="3" t="s">
+      <c r="AQ42" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>611500</v>
+      </c>
+      <c r="E43" s="3">
         <v>607500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>635000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>582900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>617000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>577100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>600200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>649800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>572100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>561700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>612000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>522700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>531100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>541400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>565500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>531900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>520800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>495900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>491000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>486500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>506800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>482400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>507900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>555300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>574100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>556500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>559800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>622400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>572600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>587000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>619300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>589500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>602000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>585700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>541900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>485400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>466800</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>436700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>531300</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>439500</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>128900</v>
+      </c>
+      <c r="E44" s="3">
         <v>119100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>130200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>126100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>117800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>101300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>147600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>140700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>93400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>106400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>120600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>92400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>83500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>117200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>115600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>136700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>113500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>108800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>59800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>55100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>91100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>107500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>66200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>76900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>95800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>81200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>144800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>92100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>134900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>119200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>122300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>112100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>142000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>149900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>124000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>79000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>136400</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>137000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>95200</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>133600</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E45" s="3">
         <v>17300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>19900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>15500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>18800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>18100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>21500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>22600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>25800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>31400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>34700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>30100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>37500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>36800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>80200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>76700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>84500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>94300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>91600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>109900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>94000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>91100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>88200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>95400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>103800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>97300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>120300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>128200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>140700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>136100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>84800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>77300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>81900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>83500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>90600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>88600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>101300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>102000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>99800</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1264700</v>
+      </c>
+      <c r="E46" s="3">
         <v>2905400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1671200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1281700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1478400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1758400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1457500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1257100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1119800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1371300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1229800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1112200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1081600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1099800</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>1034300</v>
       </c>
       <c r="R46" s="3">
         <v>1034300</v>
       </c>
       <c r="S46" s="3">
+        <v>1034300</v>
+      </c>
+      <c r="T46" s="3">
         <v>1017200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1165300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1010400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>980800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1176700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1171800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1176100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1206700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1549300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1641300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1413800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1202700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1207700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1518300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1116600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1037700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1070600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1091900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1093300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>949600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1003400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>986800</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>995400</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>1042200</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>488700</v>
+      </c>
+      <c r="E47" s="3">
         <v>492800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>414700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>402400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>386100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>369500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>366000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>388100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>343000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>347800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>367700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>25500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>38000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>36600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>39700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>46400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>36800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>35900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>33900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>25700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>23900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>24400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>26200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>29000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>29500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>29400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>21800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>23900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>24600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>26300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>26000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>27200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>28900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>29700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>4700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>4800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>4700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>4500</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>20900</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>14800</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5758900</v>
+      </c>
+      <c r="E48" s="3">
         <v>5999100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6294900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6196100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6319200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6223900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6343000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6923700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6233500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6500400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6994100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3928600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4160400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4379400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4702100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4333800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4561200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4677000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4784700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4915800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4910500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4878100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5056600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5317800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5608800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5564800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3764100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4062500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4149000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4215900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4165500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4105200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>4248700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>4297000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>4160300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>4100100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>4048400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3831200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>3648700</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>3458600</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4262800</v>
+      </c>
+      <c r="E49" s="3">
         <v>4442700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4695600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4650100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4280300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4165300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4213800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4546400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4084600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4164500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4473100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3607100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3807400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4010000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4201000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3866100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4004800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4070700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4134200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4273800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4286200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3827100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3354200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3484500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3708700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3733600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3341600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3619800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3707800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3878700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3829900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3823000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3578300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3637800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3516400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3575000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>3635600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>3630100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>3687000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>3743000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5440,8 +5554,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5562,130 +5679,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>110100</v>
+      </c>
+      <c r="E52" s="3">
         <v>89400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>46400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>41500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>42100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>45800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>44500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>45400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>43300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>45800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>40700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>31200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>32900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>34400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>174700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>148100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>152500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>158900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>156900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>160800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>163400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>155800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>156500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>151400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>156900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>145000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>145900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>140600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>143100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>143700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>155200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>150800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>150200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>149400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>139400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>148600</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>136600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>159000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>152500</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>117200</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5806,130 +5929,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12080500</v>
+      </c>
+      <c r="E54" s="3">
         <v>14132500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13326400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12759600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12682000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12723900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12569800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13293000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11937000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12535400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13218500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8828300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9249800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9700400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10151800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9428600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9772500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10107800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10120300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10356900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10560800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10057200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9769800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10189400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>11053300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11114100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8687200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9049500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9232200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9783000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>9293300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9143900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>9076800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>9205800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>8914000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>8778000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>8828800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>8611700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>8504400</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>8375900</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5972,8 +6101,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6016,740 +6146,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1215400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1355500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>436500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1255300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1072600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1138000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>414200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1165700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>930400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1036100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>466300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>492700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>729400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>810200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>806900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>675600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>759800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>659600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>642800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>616900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>624400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>669000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>720000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>585800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>660900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>637600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>684900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>616900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>589300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>480000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>453100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>428000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1008600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>887300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>966500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>977600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1057900</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>924000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1190900</v>
+      </c>
+      <c r="E58" s="3">
         <v>1046900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1076100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1849600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1412900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>997600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1046100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2197200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1879400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1941900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2107900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1048800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>729900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>843100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>952700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1165300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>884400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>682100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>700800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>741500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>663800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>767700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>808000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1127600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1038100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1065200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>745900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>431700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>370100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>369600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>547100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>606200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>334600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>12300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>300500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>545200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>413000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>142300</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>360500</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>814000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>646500</v>
+      </c>
+      <c r="E59" s="3">
         <v>724600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>761400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>554400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>808100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1297500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>783700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>762800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>655400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1049100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>666900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1347100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1401100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1476900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1219700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1031700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1060500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1542600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1149300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1311900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1289500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1554000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1184900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1166600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1699500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2073700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1749800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1842800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1114700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1631000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1191300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1392600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1436700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1935600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>875000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>838800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>765000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1153800</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>720400</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>383800</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3179900</v>
+      </c>
+      <c r="E60" s="3">
         <v>3246600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3239900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3776900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3412200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3541900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3016900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4241700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3570100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4127700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3887400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2490300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2231000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2915900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2901800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3007100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2751800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2900300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2610000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2712900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2596200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2938600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2617400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2963200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3457600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3724700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3156600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2912100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2169600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2617400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2327700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2478800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2224400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2375900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2184100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2271300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2144500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2273700</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2138800</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2121800</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5979900</v>
+      </c>
+      <c r="E61" s="3">
         <v>5722200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5020800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4511700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4749400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5086600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5179300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4745600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4272500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4486400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4943600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2736100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2987100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2779800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2915200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2700600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2897100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3161300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3247100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3497300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3578700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3418500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3555900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3644100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3560700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3627900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2074500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2696000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2757200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3034800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2944000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2949900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2966300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3210500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3141200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2860300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2841200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2801600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2692400</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2495400</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1006900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1119800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1295300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1247900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1032900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1079500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1194200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1470600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1444600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1479800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1605400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1238600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1481900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1574800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1750000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1585700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1819700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1894500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1938600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1972500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2138400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1718800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1484700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1605700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1882000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1840300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1375000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1459800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2234000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2258500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2176700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2120400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2086300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2077500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2006400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2331800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2435800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2374700</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2355700</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>2641100</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6870,8 +7019,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6992,8 +7144,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7114,130 +7269,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10505600</v>
+      </c>
+      <c r="E66" s="3">
         <v>10437900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9924600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9885700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9548000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10049800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9734200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10563100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9378200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10184100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10580900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6544800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6781000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7352800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7570800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7296800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7472100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7959700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7799200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8186400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8316700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8079400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7661500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8216600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8904100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9196700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6609900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7072000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7164900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7914900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7453200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7553700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7287900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7674300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>7335000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>7466700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>7424800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>7454300</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>7191200</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>7262400</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7280,8 +7441,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7402,8 +7564,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7524,8 +7689,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7646,8 +7814,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7768,130 +7939,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>838200</v>
+      </c>
+      <c r="E72" s="3">
         <v>2931700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2605900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2101400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2361400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1935000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2103500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1952400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1873700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1659300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1905700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1593300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1755700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1609400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1808900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1426700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1579500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1427000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1605900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1442700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1529900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1287500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1419000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1260900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1408400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1185000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1311900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1162700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1248100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1026800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1024100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>789800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>970100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>712800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>778700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>509400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>602100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>370000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>525900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>326100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8012,8 +8189,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8134,8 +8314,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8256,130 +8439,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1571700</v>
+      </c>
+      <c r="E76" s="3">
         <v>3691400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3398400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2870800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3130900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2671100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2832600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2726700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2556100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2348600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2634700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2281300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2466500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2343800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2580900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2131800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2300400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2148100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2321100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2170600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2244000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1977900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2108200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1972800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2149200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1917300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2077300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1977500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2067300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1868000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1840100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1590200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1788800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1531500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1579100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1311300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1403900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1157400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>1313300</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>1113400</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8500,135 +8689,141 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8671,86 +8866,89 @@
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3">
         <v>221800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>164700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>176300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>179300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>195000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>185200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>201200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>183700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>199900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>187600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>210200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>200400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>211900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>280800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>248900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>249700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>218800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>213400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>257000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>258000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>241600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>234400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>226400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>237300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>199500</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>201400</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8793,130 +8991,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>323400</v>
+      </c>
+      <c r="E83" s="3">
         <v>310700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>321400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>345800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>298400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>304500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>281500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>246800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>266000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>278300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>271800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>252100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>272400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>297000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>395100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>361000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>368900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>379800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>384800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>390500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>382200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>359700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>363400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>372900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>386300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>385800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>292600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>305500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>290600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>291800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>285300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>268500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>267200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>259300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>256200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>242800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>230100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>213400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>210700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>193200</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9037,8 +9239,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9159,8 +9364,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9281,8 +9489,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9403,8 +9614,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9525,130 +9739,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>651100</v>
+      </c>
+      <c r="E89" s="3">
         <v>942000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1058400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>968500</v>
       </c>
-      <c r="G89" s="3">
-        <v>710900</v>
-      </c>
       <c r="H89" s="3">
+        <v>710800</v>
+      </c>
+      <c r="I89" s="3">
         <v>968500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>932500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>949300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>652400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>824800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>731700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>672300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>498000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>596500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>730800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>571600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>483900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>536800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>623200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>680600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>585800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>574100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>736400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>487000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>593800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>668800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>620500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>680500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>449400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>679800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>647800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>555100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>432000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>569300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>588900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>517900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>515300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>426900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>629000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>444300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9691,130 +9911,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-154400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-168100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-199200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-171500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-195900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-171100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-241100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-149700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-137900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-194900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-372300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-230700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-231400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-225600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9515000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-15914600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8474000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9454700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10863000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-14622900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-162500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-146700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-279500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-154900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-203100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-174900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-216200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-203400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-202900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-103000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-117900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-164700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-154000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-207600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-228600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-344500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-355700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-355100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-2040700</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-408300</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9935,8 +10159,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10057,130 +10284,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-233500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-396000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-185000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-628400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-320900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-311200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-234600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-372000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-225700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-235600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1260700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-422200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-277700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-276000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-271500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-443200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-232100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-268300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-314600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-425100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-158100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-390200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-361000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-781200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-197400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-239000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-213000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-330700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-200600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-101200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-441900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-477900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-146600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-329500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-548300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-340200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-354300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-355000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-323400</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-405400</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10223,59 +10456,60 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="D96" s="3">
+        <v>2451000</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>631000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>525600</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>447900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>373200</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O96" s="3">
         <v>325400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>357100</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-280100</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -10283,11 +10517,11 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-298100</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -10295,23 +10529,23 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-277500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-317800</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-358600</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
@@ -10319,11 +10553,11 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-352700</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
@@ -10331,11 +10565,11 @@
         <v>0</v>
       </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-327500</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
         <v>0</v>
       </c>
@@ -10343,10 +10577,13 @@
         <v>0</v>
       </c>
       <c r="AP96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-531000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10467,8 +10704,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10589,8 +10829,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10711,166 +10954,172 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2039500</v>
+      </c>
+      <c r="E100" s="3">
         <v>763500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-552200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-509300</v>
       </c>
-      <c r="G100" s="3">
-        <v>-831100</v>
-      </c>
       <c r="H100" s="3">
+        <v>-831000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-291100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-417300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-613000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-675400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-354500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>497700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-189300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-189000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-218500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-469800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-149900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-426300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-164800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-268800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-419200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-450500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-201900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-326000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>30600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-540200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-104200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-157800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-347400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-546500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-201800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-179500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-55000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-316000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-308800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-180500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-178400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-106900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-294700</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-56200</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
@@ -10878,11 +11127,11 @@
         <v>0</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
@@ -10890,191 +11139,197 @@
         <v>0</v>
       </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>300</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
         <v>-300</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>400</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-100</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-300</v>
       </c>
-      <c r="AO101" s="3">
-        <v>0</v>
-      </c>
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1622100</v>
+      </c>
+      <c r="E102" s="3">
         <v>1309600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>321200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-169100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-441200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>366200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>280600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-35600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-248700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>234600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-31100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>60900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>31000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>102000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-21600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-174500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>103700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>39900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-163700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-22300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-18500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>49800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-264700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-142000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>323900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>250600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-298500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>377000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>26200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>21700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-30300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-69100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>37700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-17400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-35300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>11000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-17300</v>
       </c>
     </row>
